--- a/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>CBRG</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,8 +727,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,8 +774,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,40 +1093,41 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
       </c>
       <c r="I17" s="3">
+        <v>300</v>
+      </c>
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>100</v>
       </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
@@ -1111,8 +1138,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1120,31 +1150,31 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1206,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,31 +1216,31 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1217,8 +1251,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1226,23 +1263,23 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F21" s="3">
         <v>2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2500</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,40 +1345,43 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5000</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1349,8 +1392,11 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,40 +1486,43 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5000</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1481,40 +1533,43 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5000</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1768,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1710,31 +1780,31 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1745,40 +1815,43 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5000</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,40 +1909,43 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5000</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -1877,46 +1956,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,8 +2048,9 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1971,28 +2058,28 @@
         <v>0</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
@@ -2006,8 +2093,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2094,8 +2187,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,35 +2234,38 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
       </c>
       <c r="F45" s="3">
         <v>300</v>
       </c>
       <c r="G45" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>600</v>
       </c>
       <c r="I45" s="3">
+        <v>600</v>
+      </c>
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,37 +2281,40 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
+      <c r="L46" s="3">
+        <v>0</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
@@ -2226,35 +2328,38 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E47" s="3">
         <v>44200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>240400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>237800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>235900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>235000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>234700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>234600</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2270,8 +2375,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,38 +2563,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,38 +2657,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E54" s="3">
         <v>44400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>240900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>238200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>236500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>235800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>236000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>236200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,38 +2744,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,8 +2789,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2702,8 +2836,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2717,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3">
         <v>100</v>
@@ -2729,11 +2866,11 @@
         <v>100</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,8 +2883,11 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2755,29 +2895,29 @@
         <v>200</v>
       </c>
       <c r="E60" s="3">
+        <v>200</v>
+      </c>
+      <c r="F60" s="3">
         <v>100</v>
       </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
       <c r="G60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
       </c>
       <c r="I60" s="3">
+        <v>100</v>
+      </c>
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,34 +2930,37 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1400</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1000</v>
       </c>
       <c r="H61" s="3">
         <v>1000</v>
       </c>
       <c r="I61" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J61" s="3">
         <v>1100</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2834,35 +2977,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,38 +3165,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,38 +3419,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-3400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-3500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-6000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,37 +3607,40 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E76" s="3">
         <v>40700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>236800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>234000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>231600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>228900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>225700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>223200</v>
       </c>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>0</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,46 +3701,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,40 +3753,43 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5000</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
         <v>0</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3821,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,35 +4101,38 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-300</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
       </c>
       <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4169,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,8 +4308,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,23 +4562,26 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-197700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -4343,11 +4589,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>236200</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,8 +4609,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,35 +4656,38 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>100</v>
       </c>
       <c r="G102" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="H102" s="3">
         <v>-300</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4449,6 +4701,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>CBRG</t>
   </si>
@@ -656,82 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,8 +784,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -824,8 +837,14 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,8 +890,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,8 +915,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +964,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,31 +1017,37 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-300</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1031,8 +1070,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1123,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,46 +1145,48 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E17" s="3">
-        <v>600</v>
+        <v>-200</v>
       </c>
       <c r="F17" s="3">
         <v>300</v>
       </c>
       <c r="G17" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
       </c>
       <c r="I17" s="3">
+        <v>500</v>
+      </c>
+      <c r="J17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="N17" s="3">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1141,8 +1194,14 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1150,37 +1209,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-600</v>
+        <v>200</v>
       </c>
       <c r="F18" s="3">
         <v>-300</v>
       </c>
       <c r="G18" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1188,8 +1247,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,8 +1272,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1216,37 +1283,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1254,8 +1321,14 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1263,29 +1336,29 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G21" s="3">
         <v>1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1374,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,46 +1427,52 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>5000</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1480,14 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1442,8 +1533,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,46 +1586,52 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>5000</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1536,46 +1639,52 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>5000</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1583,8 +1692,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1745,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1798,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1851,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,8 +1904,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1780,37 +1919,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>200</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1818,46 +1957,52 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>5000</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -1865,8 +2010,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,46 +2063,52 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>5000</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -1959,60 +2116,72 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2199,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,8 +2220,10 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2061,31 +2234,31 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>700</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2096,8 +2269,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,8 +2322,14 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2190,8 +2375,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,41 +2428,47 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,8 +2481,14 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2293,34 +2496,34 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
+      <c r="N46" s="3">
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
@@ -2331,41 +2534,47 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F47" s="3">
         <v>44800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>44200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>240400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>237800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>235900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>235000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>234700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>234600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2378,8 +2587,14 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2425,8 +2640,14 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2472,8 +2693,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2746,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,8 +2799,14 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2592,18 +2831,18 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,8 +2852,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,44 +2905,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F54" s="3">
         <v>44900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>44400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>240900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>238200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>236500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>235800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>236000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>236200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2958,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2983,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,44 +3004,46 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,8 +3053,14 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2839,16 +3106,22 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -2857,10 +3130,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -2869,14 +3142,14 @@
         <v>100</v>
       </c>
       <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,44 +3159,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>100</v>
+      </c>
+      <c r="F60" s="3">
         <v>200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
       </c>
       <c r="H60" s="3">
         <v>100</v>
       </c>
       <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
         <v>100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>200</v>
+      </c>
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,41 +3212,47 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2980,41 +3265,47 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2400</v>
+        <v>1100</v>
       </c>
       <c r="E62" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>2400</v>
       </c>
       <c r="G62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I62" s="3">
         <v>2800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>11800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3318,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3371,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3424,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,44 +3477,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>10300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3215,8 +3530,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3555,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3604,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3657,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3710,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,44 +3763,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-4400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-3400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-3500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-3700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-6000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-11400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3816,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3869,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3922,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,43 +3975,49 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>45200</v>
+      </c>
+      <c r="F76" s="3">
         <v>40200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>40700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>236800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>234000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>231600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>228900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>225700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>223200</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
@@ -3657,8 +4028,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,98 +4081,110 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>5000</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -3803,8 +4192,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,8 +4217,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3869,8 +4266,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4319,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4372,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4425,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4478,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,41 +4531,47 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-200</v>
       </c>
       <c r="H89" s="3">
         <v>-300</v>
       </c>
       <c r="I89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4151,8 +4584,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,8 +4609,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4217,8 +4658,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4711,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,13 +4764,19 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -4325,17 +4784,17 @@
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -4358,8 +4817,14 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4842,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4891,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4944,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4997,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,41 +5050,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-197700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>236200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4612,8 +5103,14 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4659,8 +5156,14 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4668,32 +5171,32 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,6 +5207,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>CBRG</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,8 +738,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -790,8 +794,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -843,8 +850,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,20 +1040,23 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,8 +1069,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1076,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1129,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,49 +1173,50 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
         <v>500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>-200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
       <c r="O17" s="3">
         <v>0</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1200,8 +1227,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1209,40 +1239,40 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1253,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,8 +1307,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1283,40 +1317,40 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1327,8 +1361,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1336,32 +1373,32 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>3500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,49 +1473,52 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5000</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1486,8 +1529,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1539,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,49 +1641,52 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5000</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1645,49 +1697,52 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5000</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
       <c r="O27" s="3">
         <v>0</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1698,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,8 +1977,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1919,40 +1989,40 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1963,49 +2033,52 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5000</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -2016,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,49 +2145,52 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5000</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2122,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,8 +2308,9 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2240,28 +2327,28 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
+      <c r="O41" s="3">
+        <v>0</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
@@ -2275,8 +2362,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2328,8 +2418,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2381,8 +2474,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2434,44 +2530,47 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
       </c>
       <c r="J45" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
       </c>
       <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,8 +2586,11 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2496,37 +2598,37 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F46" s="3">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3">
         <v>100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1600</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
+      <c r="O46" s="3">
+        <v>0</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
@@ -2540,44 +2642,47 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E47" s="3">
         <v>11200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>44800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>44200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>240400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>237800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>235900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>235000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>234700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>234600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,8 +2698,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2646,8 +2754,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2699,8 +2810,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,8 +2922,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2837,15 +2957,15 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,47 +3034,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E54" s="3">
         <v>11200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>44900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>44400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>240900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>238200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>236500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>235800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>236000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>236200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,8 +3136,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3015,38 +3146,38 @@
         <v>300</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
         <v>0</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,8 +3190,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3112,20 +3246,23 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>600</v>
+      </c>
+      <c r="E59" s="3">
         <v>200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
       <c r="G59" s="3">
         <v>0</v>
       </c>
@@ -3136,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -3148,11 +3285,11 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
+        <v>100</v>
+      </c>
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,47 +3302,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>100</v>
-      </c>
-      <c r="F60" s="3">
-        <v>200</v>
       </c>
       <c r="G60" s="3">
         <v>200</v>
       </c>
       <c r="H60" s="3">
+        <v>200</v>
+      </c>
+      <c r="I60" s="3">
         <v>100</v>
       </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,43 +3358,46 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1000</v>
       </c>
       <c r="K61" s="3">
         <v>1000</v>
       </c>
       <c r="L61" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="M61" s="3">
         <v>1100</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3271,8 +3414,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3280,35 +3426,35 @@
         <v>1100</v>
       </c>
       <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,47 +3638,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,47 +3940,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-4400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-3400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-6000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,46 +4164,49 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>40200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>40700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>236800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>234000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>231600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>228900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>225700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>223200</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -4034,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,49 +4337,52 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5000</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
       <c r="O81" s="3">
         <v>0</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4198,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4272,8 +4471,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,8 +4751,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4549,32 +4766,32 @@
         <v>-100</v>
       </c>
       <c r="F89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-300</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
       </c>
       <c r="L89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,8 +4831,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4664,8 +4885,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,22 +4997,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>34500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -4796,8 +5026,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -4823,8 +5053,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4897,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,32 +5299,35 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-34400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-197700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -5089,11 +5335,11 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>236200</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5355,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5162,8 +5411,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5177,29 +5429,29 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>100</v>
       </c>
       <c r="I102" s="3">
         <v>100</v>
       </c>
       <c r="J102" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="K102" s="3">
         <v>-300</v>
       </c>
       <c r="L102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5213,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
